--- a/app/src/main/assets/methodmesh/odk_templates/paperbridge/example_odk_showcase_paper_form_transcribe.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/paperbridge/example_odk_showcase_paper_form_transcribe.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R80a4718d1a864825"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rc0d57f8f5b714bec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R1970e71ec13648f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rabc094741da44cdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Re39eaa6160d3498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Reacfef4a38154095"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,17 +297,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -353,18 +353,18 @@
         <x:v>paperbridge_intro</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>Paper Bridge demo</x:v>
+        <x:v>Paper Bridge transcription showcase</x:v>
       </x:c>
       <x:c r="D2" s="10" t="str">
-        <x:v>This XLSForm matches the bundled blank paper PDF and can also be imported into Paper Bridge Designer.</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str"/>
-      <x:c r="F2" s="10" t="str"/>
-      <x:c r="G2" s="10" t="str"/>
-      <x:c r="H2" s="10" t="str"/>
-      <x:c r="I2" s="10" t="str"/>
-      <x:c r="J2" s="10" t="str"/>
-      <x:c r="K2" s="10" t="str"/>
+        <x:v>Launches Paper Bridge, scans a registered paper form, and returns the declared transcription outputs plus shared MethodMesh status/audit.</x:v>
+      </x:c>
+      <x:c r="E2" s="10"/>
+      <x:c r="F2" s="10"/>
+      <x:c r="G2" s="10"/>
+      <x:c r="H2" s="10"/>
+      <x:c r="I2" s="10"/>
+      <x:c r="J2" s="10"/>
+      <x:c r="K2" s="10"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="10" t="str">
@@ -373,21 +373,21 @@
       <x:c r="B3" s="10" t="str">
         <x:v>paper_template_json</x:v>
       </x:c>
-      <x:c r="C3" s="10" t="str"/>
-      <x:c r="D3" s="10" t="str"/>
+      <x:c r="C3" s="10"/>
+      <x:c r="D3" s="10"/>
       <x:c r="E3" s="10" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F3" s="10" t="str"/>
+      <x:c r="F3" s="10"/>
       <x:c r="G3" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str"/>
-      <x:c r="I3" s="10" t="str"/>
-      <x:c r="J3" s="16" t="str">
-        <x:v>{"schema":"methodmesh.paper.v1","template_id":"paperbridge_designer_demo","version":"1","title":"Paper Bridge designer demo","page":{"width_px":1600,"height_px":2263},"anchors":{"search_fraction":0.24,"threshold_luma":150,"minimum_score":0.28},"fields":[{"name":"participant_id","label":"Participant ID","type":"ocr_text","roi":[0.18,0.15,0.52,0.188],"required":true,"regex":"[A-Za-z0-9_-]{1,24}","normalise":"trim","auto_accept":false},{"name":"visit_number","label":"Visit number","type":"ocr_integer","roi":[0.72,0.15,0.82,0.188],"required":true,"min":1,"max":12,"normalise":"trim","auto_accept":false},{"name":"eaten_today","label":"Have you eaten today?","type":"omr_single","required":true,"threshold":0.18,"min_separation":0.06,"options":[{"value":"none","label":"Nothing","roi":[0.18,0.292,0.205,0.316]},{"value":"little","label":"A little","roi":[0.18,0.332,0.205,0.356]},{"value":"some","label":"Some","roi":[0.18,0.372,0.205,0.396]},{"value":"full","label":"A full meal","roi":[0.18,0.412,0.205,0.436]}],"allowed_values":["none","little","some","full"]},{"name":"symptoms","label":"Symptoms today","type":"omr_multiple","required":false,"separator":" ","threshold":0.18,"min_separation":0.06,"options":[{"value":"fever","label":"Fever","roi":[0.18,0.515,0.205,0.539]},{"value":"cough","label":"Cough","roi":[0.52,0.515,0.545,0.539]},{"value":"diarrhoea","label":"Diarrhoea","roi":[0.18,0.558,0.205,0.582]},{"value":"headache","label":"Headache","roi":[0.52,0.558,0.545,0.582]}],"allowed_values":["fever","cough","diarrhoea","headache"]},{"name":"temperature_c","label":"Temperature (C)","type":"ocr_decimal","roi":[0.18,0.672,0.34,0.716],"required":true,"min":34.0,"max":43.0,"normalise":"trim","auto_accept":false},{"name":"specimen_barcode","label":"Specimen barcode","type":"barcode","roi":[0.54,0.655,0.84,0.755],"required":false}]}</x:v>
-      </x:c>
-      <x:c r="K3" s="10" t="str"/>
+      <x:c r="H3" s="10"/>
+      <x:c r="I3" s="10"/>
+      <x:c r="J3" s="10" t="str">
+        <x:v>{"schema":"methodmesh.paper.v1","template_id":"paperbridge_designer_demo","version":"1","title":"Paper Bridge designer demo","page":{"width_px":1760,"height_px":2423},"anchors":{"search_fraction":0.24,"threshold_luma":150,"minimum_score":0.28},"fields":[{"name":"participant_id","label":"Participant ID","type":"ocr_text","roi":[0.183232,0.161693,0.519798,0.198446],"required":true,"regex":"[A-Za-z0-9 _-]{1,40}","normalise":"trim","auto_accept":false,"constraint_expression":"regex(., '^[A-Za-z0-9 _-]{1,40}$')","constraint_message":"Use 1-40 letters, numbers, spaces, underscore or hyphen."},{"name":"visit_number","label":"Visit number","type":"ocr_integer","roi":[0.717777,0.161693,0.816768,0.198446],"required":true,"min":1,"max":12,"normalise":"trim","auto_accept":false,"constraint_expression":". &gt;= 1 and . &lt;= 12","constraint_message":"Enter 1-12."},{"name":"eaten_today","label":"Have you eaten today?","type":"omr_single","required":true,"threshold":0.18,"min_separation":0.06,"options":[{"value":"none","label":"Nothing","roi":[0.183232,0.299033,0.20798,0.322245]},{"value":"little","label":"A little","roi":[0.183232,0.33772,0.20798,0.360932]},{"value":"some","label":"Some","roi":[0.183232,0.376408,0.20798,0.39962]},{"value":"full","label":"A full meal","roi":[0.183232,0.415095,0.20798,0.438307]}],"allowed_values":["none","little","some","full"]},{"name":"symptoms","label":"Symptoms today","type":"omr_multiple","required":false,"separator":" ","threshold":0.18,"min_separation":0.06,"options":[{"value":"fever","label":"Fever","roi":[0.183232,0.514714,0.20798,0.537926]},{"value":"cough","label":"Cough","roi":[0.519798,0.514714,0.544545,0.537926]},{"value":"diarrhoea","label":"Diarrhoea","roi":[0.183232,0.556302,0.20798,0.579515]},{"value":"headache","label":"Headache","roi":[0.519798,0.556302,0.544545,0.579515]}],"allowed_values":["fever","cough","diarrhoea","headache"]},{"name":"temperature_c","label":"Temperature (C)","type":"ocr_decimal","roi":[0.183232,0.666562,0.341616,0.709118],"required":true,"min":34.0,"max":43.0,"normalise":"trim","auto_accept":false,"constraint_expression":". &gt;= 34 and . &lt;= 43","constraint_message":"Temperature must be 34-43 C."},{"name":"specimen_barcode","label":"Specimen barcode","type":"barcode","roi":[0.539596,0.650119,0.836566,0.746837],"required":false},{"name":"site_sketch","label":"Site sketch / drawing","type":"image","roi":[0.119225,0.743123,0.313533,0.787881],"required":false,"auto_accept":true}],"coordinate_frame":"canonical_page","authoring_profile":{"schema":"methodmesh.paper.colour.v1","scalar_envelope":"#D81B60","select_one_envelope":"#00897B","select_multiple_envelope":"#EF6C00","barcode_envelope":"#5E35B1","choice_label":"#1565C0","question_text":"#000000","response_geometry":"#000000","authoring_text_style":"bold_recommended","runtime_colour_required":false,"image_envelope":"#7CB342"},"registration":{"type":"apriltag8","family":"tag36h11","schema_key":"DEMO01","marker_size_fraction":0.065,"ids":[0,1,2,3,4,5,6,7],"centres":[[0.06,0.06],[0.5,0.06],[0.94,0.06],[0.06,0.5],[0.94,0.5],[0.06,0.94],[0.5,0.94],[0.94,0.94]]}}</x:v>
+      </x:c>
+      <x:c r="K3" s="10"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="12" t="str">
@@ -400,18 +400,18 @@
         <x:v>Scan paper questionnaire</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
-        <x:v>Launch Paper Bridge and return the six mapped fields.</x:v>
+        <x:v>Paper Bridge returns named values and media to this group. ODK owns the form instance and submission.</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str"/>
-      <x:c r="G4" s="12" t="str"/>
-      <x:c r="H4" s="12" t="str"/>
-      <x:c r="I4" s="12" t="str"/>
-      <x:c r="J4" s="12" t="str"/>
+      <x:c r="F4" s="12"/>
+      <x:c r="G4" s="12"/>
+      <x:c r="H4" s="12"/>
+      <x:c r="I4" s="12"/>
+      <x:c r="J4" s="12"/>
       <x:c r="K4" s="12" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='paper.form.transcribe',input_paper_template_json=${paper_template_json},input_source_mode='camera',input_auto_accept_omr='true',input_auto_accept_ocr='false',input_return_source_image='true',input_return_rectified_image='true',input_payload_mode='FULL',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='paper.form.transcribe',input_paper_template_json=${paper_template_json},input_source_mode='camera',input_auto_accept_omr='true',input_auto_accept_ocr='false',input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -424,7 +424,7 @@
       <x:c r="C5" s="14" t="str">
         <x:v>Participant ID</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="str"/>
+      <x:c r="D5" s="14"/>
       <x:c r="E5" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
@@ -435,13 +435,13 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
-        <x:v>regex(., '^[A-Za-z0-9_-]{1,24}$')</x:v>
+        <x:v>regex(., '^[A-Za-z0-9 _-]{1,40}$')</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>Use 1-24 letters, numbers, underscore or hyphen.</x:v>
-      </x:c>
-      <x:c r="J5" s="14" t="str"/>
-      <x:c r="K5" s="14" t="str"/>
+        <x:v>Use 1-40 letters, numbers, spaces, underscore or hyphen.</x:v>
+      </x:c>
+      <x:c r="J5" s="14"/>
+      <x:c r="K5" s="14"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -453,7 +453,7 @@
       <x:c r="C6" s="14" t="str">
         <x:v>Visit number</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="str"/>
+      <x:c r="D6" s="14"/>
       <x:c r="E6" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
@@ -467,10 +467,10 @@
         <x:v>. &gt;= 1 and . &lt;= 12</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>Enter a visit number from 1 to 12.</x:v>
-      </x:c>
-      <x:c r="J6" s="14" t="str"/>
-      <x:c r="K6" s="14" t="str"/>
+        <x:v>Enter 1-12.</x:v>
+      </x:c>
+      <x:c r="J6" s="14"/>
+      <x:c r="K6" s="14"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -482,7 +482,7 @@
       <x:c r="C7" s="14" t="str">
         <x:v>Have you eaten today?</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="str"/>
+      <x:c r="D7" s="14"/>
       <x:c r="E7" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
@@ -492,10 +492,10 @@
       <x:c r="G7" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="str"/>
-      <x:c r="I7" s="14" t="str"/>
-      <x:c r="J7" s="14" t="str"/>
-      <x:c r="K7" s="14" t="str"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="14"/>
+      <x:c r="K7" s="14"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
@@ -507,18 +507,18 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Symptoms today</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="str"/>
+      <x:c r="D8" s="14"/>
       <x:c r="E8" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="str"/>
+      <x:c r="F8" s="14"/>
       <x:c r="G8" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="str"/>
-      <x:c r="I8" s="14" t="str"/>
-      <x:c r="J8" s="14" t="str"/>
-      <x:c r="K8" s="14" t="str"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="J8" s="14"/>
+      <x:c r="K8" s="14"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -530,7 +530,7 @@
       <x:c r="C9" s="14" t="str">
         <x:v>Temperature (C)</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="str"/>
+      <x:c r="D9" s="14"/>
       <x:c r="E9" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
@@ -544,10 +544,10 @@
         <x:v>. &gt;= 34 and . &lt;= 43</x:v>
       </x:c>
       <x:c r="I9" s="14" t="str">
-        <x:v>Temperature must be between 34 and 43 C.</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="str"/>
-      <x:c r="K9" s="14" t="str"/>
+        <x:v>Temperature must be 34-43 C.</x:v>
+      </x:c>
+      <x:c r="J9" s="14"/>
+      <x:c r="K9" s="14"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
@@ -559,148 +559,675 @@
       <x:c r="C10" s="14" t="str">
         <x:v>Specimen barcode</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="str"/>
+      <x:c r="D10" s="14"/>
       <x:c r="E10" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="str"/>
+      <x:c r="F10" s="14"/>
       <x:c r="G10" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="str"/>
-      <x:c r="I10" s="14" t="str"/>
-      <x:c r="J10" s="14" t="str"/>
-      <x:c r="K10" s="14" t="str"/>
+      <x:c r="H10" s="14"/>
+      <x:c r="I10" s="14"/>
+      <x:c r="J10" s="14"/>
+      <x:c r="K10" s="14"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>text</x:v>
+        <x:v>image</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>paper_status</x:v>
+        <x:v>site_sketch</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>Paper Bridge status</x:v>
-      </x:c>
-      <x:c r="D11" s="14" t="str"/>
+        <x:v>Site sketch / drawing</x:v>
+      </x:c>
+      <x:c r="D11" s="14"/>
       <x:c r="E11" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="str"/>
+      <x:c r="F11" s="14"/>
       <x:c r="G11" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H11" s="14" t="str"/>
-      <x:c r="I11" s="14" t="str"/>
-      <x:c r="J11" s="14" t="str"/>
-      <x:c r="K11" s="14" t="str"/>
+      <x:c r="H11" s="14"/>
+      <x:c r="I11" s="14"/>
+      <x:c r="J11" s="14"/>
+      <x:c r="K11" s="14"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>image</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>paper_source_image</x:v>
+        <x:v>paper_status</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>Captured source page</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="str"/>
+        <x:v>Paper Bridge status</x:v>
+      </x:c>
+      <x:c r="D12" s="14"/>
       <x:c r="E12" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="str"/>
+      <x:c r="F12" s="14"/>
       <x:c r="G12" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="str"/>
-      <x:c r="I12" s="14" t="str"/>
-      <x:c r="J12" s="14" t="str"/>
-      <x:c r="K12" s="14" t="str"/>
+      <x:c r="H12" s="14"/>
+      <x:c r="I12" s="14"/>
+      <x:c r="J12" s="14"/>
+      <x:c r="K12" s="14"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>image</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>paper_rectified_image</x:v>
+        <x:v>paper_template_id</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Rectified page</x:v>
-      </x:c>
-      <x:c r="D13" s="14" t="str"/>
+        <x:v>Paper template ID</x:v>
+      </x:c>
+      <x:c r="D13" s="14"/>
       <x:c r="E13" s="14" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="str"/>
+      <x:c r="F13" s="14"/>
       <x:c r="G13" s="14" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="str"/>
-      <x:c r="I13" s="14" t="str"/>
-      <x:c r="J13" s="14" t="str"/>
-      <x:c r="K13" s="14" t="str"/>
+      <x:c r="H13" s="14"/>
+      <x:c r="I13" s="14"/>
+      <x:c r="J13" s="14"/>
+      <x:c r="K13" s="14"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>paper_template_version</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>MethodMesh full JSON</x:v>
-      </x:c>
-      <x:c r="D14" s="10" t="str"/>
+        <x:v>Paper template version</x:v>
+      </x:c>
+      <x:c r="D14" s="10"/>
       <x:c r="E14" s="10" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F14" s="10" t="str"/>
+      <x:c r="F14" s="10"/>
       <x:c r="G14" s="10" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="H14" s="10" t="str"/>
-      <x:c r="I14" s="10" t="str"/>
-      <x:c r="J14" s="10" t="str"/>
-      <x:c r="K14" s="10" t="str"/>
+      <x:c r="H14" s="10"/>
+      <x:c r="I14" s="10"/>
+      <x:c r="J14" s="10"/>
+      <x:c r="K14" s="10"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="10" t="str">
-        <x:v>end_group</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>scan_paper_end</x:v>
-      </x:c>
-      <x:c r="C15" s="10" t="str"/>
-      <x:c r="D15" s="10" t="str"/>
-      <x:c r="E15" s="10" t="str"/>
-      <x:c r="F15" s="10" t="str"/>
-      <x:c r="G15" s="10" t="str"/>
-      <x:c r="H15" s="10" t="str"/>
-      <x:c r="I15" s="10" t="str"/>
-      <x:c r="J15" s="10" t="str"/>
-      <x:c r="K15" s="10" t="str"/>
+        <x:v>paper_values_json</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>Paper values JSON</x:v>
+      </x:c>
+      <x:c r="D15" s="10"/>
+      <x:c r="E15" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F15" s="10"/>
+      <x:c r="G15" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H15" s="10"/>
+      <x:c r="I15" s="10"/>
+      <x:c r="J15" s="10"/>
+      <x:c r="K15" s="10"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>paper_dynamic_fields_json</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>Dynamic fields JSON</x:v>
+      </x:c>
+      <x:c r="D16" s="10"/>
+      <x:c r="E16" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F16" s="10"/>
+      <x:c r="G16" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H16" s="10"/>
+      <x:c r="I16" s="10"/>
+      <x:c r="J16" s="10"/>
+      <x:c r="K16" s="10"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>paper_field_count</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>Paper field count</x:v>
+      </x:c>
+      <x:c r="D17" s="10"/>
+      <x:c r="E17" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F17" s="10"/>
+      <x:c r="G17" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H17" s="10"/>
+      <x:c r="I17" s="10"/>
+      <x:c r="J17" s="10"/>
+      <x:c r="K17" s="10"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>paper_auto_accepted_count</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>Auto-accepted count</x:v>
+      </x:c>
+      <x:c r="D18" s="10"/>
+      <x:c r="E18" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F18" s="10"/>
+      <x:c r="G18" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H18" s="10"/>
+      <x:c r="I18" s="10"/>
+      <x:c r="J18" s="10"/>
+      <x:c r="K18" s="10"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>paper_reviewed_count</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>Reviewed count</x:v>
+      </x:c>
+      <x:c r="D19" s="10"/>
+      <x:c r="E19" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F19" s="10"/>
+      <x:c r="G19" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H19" s="10"/>
+      <x:c r="I19" s="10"/>
+      <x:c r="J19" s="10"/>
+      <x:c r="K19" s="10"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>paper_unresolved_count</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>Unresolved count</x:v>
+      </x:c>
+      <x:c r="D20" s="10"/>
+      <x:c r="E20" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F20" s="10"/>
+      <x:c r="G20" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H20" s="10"/>
+      <x:c r="I20" s="10"/>
+      <x:c r="J20" s="10"/>
+      <x:c r="K20" s="10"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
+        <x:v>image</x:v>
+      </x:c>
+      <x:c r="B21" s="10" t="str">
+        <x:v>paper_source_image</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>Source paper scan</x:v>
+      </x:c>
+      <x:c r="D21" s="10"/>
+      <x:c r="E21" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F21" s="10"/>
+      <x:c r="G21" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H21" s="10"/>
+      <x:c r="I21" s="10"/>
+      <x:c r="J21" s="10"/>
+      <x:c r="K21" s="10"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
+        <x:v>image</x:v>
+      </x:c>
+      <x:c r="B22" s="10" t="str">
+        <x:v>paper_rectified_image</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>Registered analysis page</x:v>
+      </x:c>
+      <x:c r="D22" s="10"/>
+      <x:c r="E22" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F22" s="10"/>
+      <x:c r="G22" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H22" s="10"/>
+      <x:c r="I22" s="10"/>
+      <x:c r="J22" s="10"/>
+      <x:c r="K22" s="10"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B23" s="10" t="str">
+        <x:v>paper_template_sha256</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>Template SHA-256</x:v>
+      </x:c>
+      <x:c r="D23" s="10"/>
+      <x:c r="E23" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F23" s="10"/>
+      <x:c r="G23" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H23" s="10"/>
+      <x:c r="I23" s="10"/>
+      <x:c r="J23" s="10"/>
+      <x:c r="K23" s="10"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B24" s="10" t="str">
+        <x:v>paper_source_sha256</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>Source image SHA-256</x:v>
+      </x:c>
+      <x:c r="D24" s="10"/>
+      <x:c r="E24" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F24" s="10"/>
+      <x:c r="G24" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H24" s="10"/>
+      <x:c r="I24" s="10"/>
+      <x:c r="J24" s="10"/>
+      <x:c r="K24" s="10"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B25" s="10" t="str">
+        <x:v>paper_rectified_sha256</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>Registered image SHA-256</x:v>
+      </x:c>
+      <x:c r="D25" s="10"/>
+      <x:c r="E25" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F25" s="10"/>
+      <x:c r="G25" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H25" s="10"/>
+      <x:c r="I25" s="10"/>
+      <x:c r="J25" s="10"/>
+      <x:c r="K25" s="10"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>paper_extraction_audit_json</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>Extraction audit JSON</x:v>
+      </x:c>
+      <x:c r="D26" s="10"/>
+      <x:c r="E26" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F26" s="10"/>
+      <x:c r="G26" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H26" s="10"/>
+      <x:c r="I26" s="10"/>
+      <x:c r="J26" s="10"/>
+      <x:c r="K26" s="10"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>paper_manual_edits_json</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>Manual edit audit JSON</x:v>
+      </x:c>
+      <x:c r="D27" s="10"/>
+      <x:c r="E27" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F27" s="10"/>
+      <x:c r="G27" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H27" s="10"/>
+      <x:c r="I27" s="10"/>
+      <x:c r="J27" s="10"/>
+      <x:c r="K27" s="10"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>paper_manual_edit_count</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>Manual edit count</x:v>
+      </x:c>
+      <x:c r="D28" s="10"/>
+      <x:c r="E28" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F28" s="10"/>
+      <x:c r="G28" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H28" s="10"/>
+      <x:c r="I28" s="10"/>
+      <x:c r="J28" s="10"/>
+      <x:c r="K28" s="10"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>paper_logic_checks_json</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>XLSForm logic checks JSON</x:v>
+      </x:c>
+      <x:c r="D29" s="10"/>
+      <x:c r="E29" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F29" s="10"/>
+      <x:c r="G29" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H29" s="10"/>
+      <x:c r="I29" s="10"/>
+      <x:c r="J29" s="10"/>
+      <x:c r="K29" s="10"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>paper_logic_violation_count</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>Logic violation count</x:v>
+      </x:c>
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F30" s="10"/>
+      <x:c r="G30" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H30" s="10"/>
+      <x:c r="I30" s="10"/>
+      <x:c r="J30" s="10"/>
+      <x:c r="K30" s="10"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="10" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>paper_logic_unknown_count</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>Logic unknown count</x:v>
+      </x:c>
+      <x:c r="D31" s="10"/>
+      <x:c r="E31" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F31" s="10"/>
+      <x:c r="G31" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H31" s="10"/>
+      <x:c r="I31" s="10"/>
+      <x:c r="J31" s="10"/>
+      <x:c r="K31" s="10"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="str">
+        <x:v>paper_na_fields_json</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>NA override fields JSON</x:v>
+      </x:c>
+      <x:c r="D32" s="10"/>
+      <x:c r="E32" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F32" s="10"/>
+      <x:c r="G32" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H32" s="10"/>
+      <x:c r="I32" s="10"/>
+      <x:c r="J32" s="10"/>
+      <x:c r="K32" s="10"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B33" s="10" t="str">
+        <x:v>paper_attachment_metadata_json</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>Attachment metadata JSON</x:v>
+      </x:c>
+      <x:c r="D33" s="10"/>
+      <x:c r="E33" s="10" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F33" s="10"/>
+      <x:c r="G33" s="10" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H33" s="10"/>
+      <x:c r="I33" s="10"/>
+      <x:c r="J33" s="10"/>
+      <x:c r="K33" s="10"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>paper_scan_time_iso</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Paper scan time</x:v>
+      </x:c>
+      <x:c r="D34"/>
+      <x:c r="E34" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H34"/>
+      <x:c r="I34"/>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>paper_error</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Paper Bridge error</x:v>
+      </x:c>
+      <x:c r="D35"/>
+      <x:c r="E35" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H35"/>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>methodmesh_status</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>MethodMesh status</x:v>
+      </x:c>
+      <x:c r="D36"/>
+      <x:c r="E36" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F36"/>
+      <x:c r="G36" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H36"/>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>MethodMesh full JSON</x:v>
+      </x:c>
+      <x:c r="D37"/>
+      <x:c r="E37" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F37"/>
+      <x:c r="G37" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="H37"/>
+      <x:c r="I37"/>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
+      <x:c r="I38"/>
+      <x:c r="J38"/>
+      <x:c r="K38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
         <x:v>note</x:v>
       </x:c>
-      <x:c r="B16" s="10" t="str">
+      <x:c r="B39" t="str">
         <x:v>paperbridge_done</x:v>
       </x:c>
-      <x:c r="C16" s="10" t="str">
-        <x:v>Paper transcription complete</x:v>
-      </x:c>
-      <x:c r="D16" s="10" t="str">
-        <x:v>Returned values remain in this ODK form instance; ODK/Collect owns validation, finalization and Central submission.</x:v>
-      </x:c>
-      <x:c r="E16" s="10" t="str"/>
-      <x:c r="F16" s="10" t="str"/>
-      <x:c r="G16" s="10" t="str"/>
-      <x:c r="H16" s="10" t="str"/>
-      <x:c r="I16" s="10" t="str"/>
-      <x:c r="J16" s="10" t="str"/>
-      <x:c r="K16" s="10" t="str"/>
+      <x:c r="C39" t="str">
+        <x:v>Paper transcription returned</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Participant: ${participant_id} · visit ${visit_number} · eaten: ${eaten_today} · symptoms: ${symptoms} · temperature: ${temperature_c} · barcode: ${specimen_barcode}</x:v>
+      </x:c>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
+      <x:c r="I39"/>
+      <x:c r="J39"/>
+      <x:c r="K39"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -827,7 +1354,7 @@
     <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -845,16 +1372,16 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>Paper Bridge designer demo</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>paperbridge_designer_demo</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="A2" s="10" t="str">
+        <x:v>Paper Bridge transcription showcase</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>paperbridge_form_transcribe_showcase</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>2026091101</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
         <x:v>concat('PB-', ${participant_id}, '-', ${visit_number})</x:v>
       </x:c>
     </x:row>
